--- a/templates/template_horeca_products.xlsx
+++ b/templates/template_horeca_products.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Bot\Market_Survey\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F8C31F4-94BE-4630-BEF6-6761D6C1BEB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B633A6E-9B0C-4B6C-98A9-7F8064B548FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="85">
   <si>
     <t>Dealer :                                                      Report Date:</t>
   </si>
@@ -140,9 +140,6 @@
   </si>
   <si>
     <t>WURKZ</t>
-  </si>
-  <si>
-    <t>CAMBODIA ED</t>
   </si>
   <si>
     <t>DAZZ</t>
@@ -441,8 +438,8 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -450,13 +447,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -466,20 +456,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -487,7 +472,19 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -723,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA48"/>
+  <dimension ref="A1:AA46"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -750,8 +747,8 @@
       <c r="D1" s="7"/>
     </row>
     <row r="2" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="28" t="s">
-        <v>73</v>
+      <c r="A2" s="10" t="s">
+        <v>72</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -781,7 +778,7 @@
       <c r="AA2" s="11"/>
     </row>
     <row r="3" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="18" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="11"/>
@@ -812,18 +809,18 @@
       <c r="AA3" s="11"/>
     </row>
     <row r="4" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="19" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="14"/>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="19" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
       <c r="G4" s="14"/>
-      <c r="H4" s="15" t="s">
+      <c r="H4" s="19" t="s">
         <v>3</v>
       </c>
       <c r="I4" s="13"/>
@@ -840,7 +837,7 @@
       <c r="T4" s="13"/>
       <c r="U4" s="13"/>
       <c r="V4" s="14"/>
-      <c r="W4" s="15" t="s">
+      <c r="W4" s="19" t="s">
         <v>4</v>
       </c>
       <c r="X4" s="13"/>
@@ -849,7 +846,7 @@
       <c r="AA4" s="14"/>
     </row>
     <row r="5" spans="1:27" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="24" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="13"/>
@@ -886,43 +883,43 @@
       <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="28" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
       <c r="G6" s="14"/>
-      <c r="H6" s="21" t="s">
+      <c r="H6" s="20" t="s">
         <v>9</v>
       </c>
       <c r="I6" s="13"/>
       <c r="J6" s="13"/>
       <c r="K6" s="14"/>
-      <c r="L6" s="21" t="s">
+      <c r="L6" s="20" t="s">
         <v>10</v>
       </c>
       <c r="M6" s="13"/>
       <c r="N6" s="13"/>
       <c r="O6" s="14"/>
-      <c r="P6" s="21" t="s">
+      <c r="P6" s="20" t="s">
         <v>11</v>
       </c>
       <c r="Q6" s="13"/>
       <c r="R6" s="13"/>
       <c r="S6" s="14"/>
-      <c r="T6" s="21" t="s">
+      <c r="T6" s="20" t="s">
         <v>12</v>
       </c>
       <c r="U6" s="13"/>
       <c r="V6" s="14"/>
-      <c r="W6" s="16" t="s">
+      <c r="W6" s="27" t="s">
         <v>13</v>
       </c>
       <c r="X6" s="13"/>
       <c r="Y6" s="14"/>
       <c r="Z6" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AA6" s="8" t="s">
         <v>14</v>
@@ -966,7 +963,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C8" s="12"/>
       <c r="D8" s="13"/>
@@ -1032,7 +1029,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C10" s="12"/>
       <c r="D10" s="13"/>
@@ -1067,29 +1064,29 @@
       <c r="B11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
-      <c r="K11" s="20"/>
-      <c r="L11" s="18"/>
-      <c r="M11" s="19"/>
-      <c r="N11" s="19"/>
-      <c r="O11" s="20"/>
-      <c r="P11" s="18"/>
-      <c r="Q11" s="19"/>
-      <c r="R11" s="19"/>
-      <c r="S11" s="20"/>
-      <c r="T11" s="18"/>
-      <c r="U11" s="19"/>
-      <c r="V11" s="20"/>
-      <c r="W11" s="18"/>
-      <c r="X11" s="19"/>
-      <c r="Y11" s="20"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="17"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+      <c r="K11" s="17"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="17"/>
+      <c r="P11" s="15"/>
+      <c r="Q11" s="16"/>
+      <c r="R11" s="16"/>
+      <c r="S11" s="17"/>
+      <c r="T11" s="15"/>
+      <c r="U11" s="16"/>
+      <c r="V11" s="17"/>
+      <c r="W11" s="15"/>
+      <c r="X11" s="16"/>
+      <c r="Y11" s="17"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
     </row>
@@ -1225,7 +1222,7 @@
       <c r="Z15" s="3"/>
       <c r="AA15" s="3"/>
     </row>
-    <row r="16" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:27" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A16" s="3">
         <v>10</v>
       </c>
@@ -1258,7 +1255,7 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
     </row>
-    <row r="17" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:27" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A17" s="3">
         <v>11</v>
       </c>
@@ -1291,7 +1288,7 @@
       <c r="Z17" s="3"/>
       <c r="AA17" s="3"/>
     </row>
-    <row r="18" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:27" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="3">
         <v>12</v>
       </c>
@@ -1336,10 +1333,10 @@
       <c r="E19" s="13"/>
       <c r="F19" s="13"/>
       <c r="G19" s="14"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="14"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="17"/>
       <c r="L19" s="12"/>
       <c r="M19" s="13"/>
       <c r="N19" s="13"/>
@@ -1362,17 +1359,17 @@
         <v>14</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="C20" s="12"/>
       <c r="D20" s="13"/>
       <c r="E20" s="13"/>
       <c r="F20" s="13"/>
       <c r="G20" s="14"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="19"/>
-      <c r="K20" s="20"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="13"/>
+      <c r="J20" s="13"/>
+      <c r="K20" s="14"/>
       <c r="L20" s="12"/>
       <c r="M20" s="13"/>
       <c r="N20" s="13"/>
@@ -1395,7 +1392,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="13"/>
@@ -1490,158 +1487,162 @@
       <c r="AA23" s="3"/>
     </row>
     <row r="24" spans="1:27" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="3">
+      <c r="A24" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="11"/>
+      <c r="P24" s="11"/>
+      <c r="Q24" s="11"/>
+      <c r="R24" s="11"/>
+      <c r="S24" s="11"/>
+      <c r="T24" s="11"/>
+      <c r="U24" s="11"/>
+      <c r="V24" s="11"/>
+      <c r="W24" s="11"/>
+      <c r="X24" s="11"/>
+      <c r="Y24" s="11"/>
+      <c r="Z24" s="11"/>
+      <c r="AA24" s="11"/>
+    </row>
+    <row r="25" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="E25" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="L25" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="M25" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="N25" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="O25" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="P25" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q25" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="R25" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="S25" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="T25" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="U25" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="V25" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="W25" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="X25" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="Y25" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z25" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="AA25" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="3">
+        <v>1</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="3"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="3"/>
+      <c r="M26" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C24" s="12"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="13"/>
-      <c r="J24" s="13"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="12"/>
-      <c r="M24" s="13"/>
-      <c r="N24" s="13"/>
-      <c r="O24" s="14"/>
-      <c r="P24" s="12"/>
-      <c r="Q24" s="13"/>
-      <c r="R24" s="13"/>
-      <c r="S24" s="14"/>
-      <c r="T24" s="12"/>
-      <c r="U24" s="13"/>
-      <c r="V24" s="14"/>
-      <c r="W24" s="12"/>
-      <c r="X24" s="13"/>
-      <c r="Y24" s="14"/>
-      <c r="Z24" s="3"/>
-      <c r="AA24" s="3"/>
-    </row>
-    <row r="25" spans="1:27" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="11"/>
-      <c r="N25" s="11"/>
-      <c r="O25" s="11"/>
-      <c r="P25" s="11"/>
-      <c r="Q25" s="11"/>
-      <c r="R25" s="11"/>
-      <c r="S25" s="11"/>
-      <c r="T25" s="11"/>
-      <c r="U25" s="11"/>
-      <c r="V25" s="11"/>
-      <c r="W25" s="11"/>
-      <c r="X25" s="11"/>
-      <c r="Y25" s="11"/>
-      <c r="Z25" s="11"/>
-      <c r="AA25" s="11"/>
-    </row>
-    <row r="26" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="K26" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="L26" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="M26" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="N26" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="O26" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="P26" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="Q26" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="R26" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="S26" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="T26" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="U26" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="V26" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="W26" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="X26" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="Y26" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z26" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA26" s="4" t="s">
-        <v>20</v>
-      </c>
+      <c r="N26" s="3"/>
+      <c r="O26" s="3"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="3"/>
+      <c r="R26" s="1"/>
+      <c r="S26" s="3"/>
+      <c r="T26" s="3"/>
+      <c r="U26" s="3"/>
+      <c r="V26" s="3"/>
+      <c r="W26" s="1"/>
+      <c r="X26" s="3"/>
+      <c r="Y26" s="3"/>
+      <c r="Z26" s="3"/>
+      <c r="AA26" s="3"/>
     </row>
     <row r="27" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
@@ -1649,25 +1650,29 @@
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="1" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="1" t="s">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="N27" s="3"/>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
-      <c r="R27" s="1"/>
+      <c r="R27" s="1" t="s">
+        <v>75</v>
+      </c>
       <c r="S27" s="3"/>
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
       <c r="V27" s="3"/>
-      <c r="W27" s="1"/>
+      <c r="W27" s="1" t="s">
+        <v>77</v>
+      </c>
       <c r="X27" s="3"/>
       <c r="Y27" s="3"/>
       <c r="Z27" s="3"/>
@@ -1675,7 +1680,7 @@
     </row>
     <row r="28" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>74</v>
@@ -1686,40 +1691,38 @@
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="1" t="s">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="N28" s="3"/>
       <c r="O28" s="3"/>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
       <c r="R28" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="S28" s="3"/>
       <c r="T28" s="3"/>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
-      <c r="W28" s="1" t="s">
-        <v>78</v>
-      </c>
+      <c r="W28" s="1"/>
       <c r="X28" s="3"/>
       <c r="Y28" s="3"/>
       <c r="Z28" s="3"/>
       <c r="AA28" s="3"/>
     </row>
-    <row r="29" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:27" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A29" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>75</v>
+        <v>34</v>
       </c>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
@@ -1727,21 +1730,21 @@
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="1" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="1" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="N29" s="3"/>
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
       <c r="R29" s="1" t="s">
-        <v>82</v>
+        <v>50</v>
       </c>
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
@@ -1755,10 +1758,10 @@
     </row>
     <row r="30" spans="1:27" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A30" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
@@ -1766,21 +1769,21 @@
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="1" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N30" s="3"/>
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
       <c r="R30" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
@@ -1794,10 +1797,10 @@
     </row>
     <row r="31" spans="1:27" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>35</v>
+        <v>84</v>
       </c>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
@@ -1805,38 +1808,40 @@
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="1" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N31" s="3"/>
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
       <c r="Q31" s="3"/>
       <c r="R31" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="S31" s="3"/>
       <c r="T31" s="3"/>
       <c r="U31" s="3"/>
       <c r="V31" s="3"/>
-      <c r="W31" s="1"/>
+      <c r="W31" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="X31" s="3"/>
       <c r="Y31" s="3"/>
       <c r="Z31" s="3"/>
       <c r="AA31" s="3"/>
     </row>
-    <row r="32" spans="1:27" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>85</v>
+        <v>37</v>
       </c>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
@@ -1844,29 +1849,23 @@
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
-      <c r="M32" s="1" t="s">
-        <v>55</v>
-      </c>
+      <c r="M32" s="1"/>
       <c r="N32" s="3"/>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
       <c r="Q32" s="3"/>
-      <c r="R32" s="1" t="s">
-        <v>56</v>
-      </c>
+      <c r="R32" s="1"/>
       <c r="S32" s="3"/>
       <c r="T32" s="3"/>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
-      <c r="W32" s="1" t="s">
-        <v>57</v>
-      </c>
+      <c r="W32" s="1"/>
       <c r="X32" s="3"/>
       <c r="Y32" s="3"/>
       <c r="Z32" s="3"/>
@@ -1874,10 +1873,10 @@
     </row>
     <row r="33" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
@@ -1891,7 +1890,9 @@
       <c r="J33" s="3"/>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
-      <c r="M33" s="1"/>
+      <c r="M33" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="N33" s="3"/>
       <c r="O33" s="3"/>
       <c r="P33" s="3"/>
@@ -1907,12 +1908,12 @@
       <c r="Z33" s="3"/>
       <c r="AA33" s="3"/>
     </row>
-    <row r="34" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:27" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
@@ -1926,14 +1927,14 @@
       <c r="J34" s="3"/>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
-      <c r="M34" s="1" t="s">
-        <v>80</v>
-      </c>
+      <c r="M34" s="1"/>
       <c r="N34" s="3"/>
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
       <c r="Q34" s="3"/>
-      <c r="R34" s="1"/>
+      <c r="R34" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
       <c r="U34" s="3"/>
@@ -1944,12 +1945,12 @@
       <c r="Z34" s="3"/>
       <c r="AA34" s="3"/>
     </row>
-    <row r="35" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:27" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
@@ -1957,7 +1958,7 @@
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
       <c r="H35" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I35" s="3"/>
       <c r="J35" s="3"/>
@@ -1969,7 +1970,7 @@
       <c r="P35" s="3"/>
       <c r="Q35" s="3"/>
       <c r="R35" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="S35" s="3"/>
       <c r="T35" s="3"/>
@@ -1983,17 +1984,19 @@
     </row>
     <row r="36" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
-      <c r="H36" s="1"/>
+      <c r="H36" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
       <c r="K36" s="3"/>
@@ -2016,10 +2019,10 @@
     </row>
     <row r="37" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
@@ -2027,19 +2030,21 @@
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
       <c r="H37" s="1" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
-      <c r="M37" s="1"/>
+      <c r="M37" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="N37" s="3"/>
       <c r="O37" s="3"/>
       <c r="P37" s="3"/>
       <c r="Q37" s="3"/>
       <c r="R37" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="S37" s="3"/>
       <c r="T37" s="3"/>
@@ -2053,10 +2058,10 @@
     </row>
     <row r="38" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
@@ -2064,18 +2069,22 @@
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
       <c r="H38" s="1" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
-      <c r="M38" s="1"/>
+      <c r="M38" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="N38" s="3"/>
       <c r="O38" s="3"/>
       <c r="P38" s="3"/>
       <c r="Q38" s="3"/>
-      <c r="R38" s="1"/>
+      <c r="R38" s="1" t="s">
+        <v>67</v>
+      </c>
       <c r="S38" s="3"/>
       <c r="T38" s="3"/>
       <c r="U38" s="3"/>
@@ -2088,10 +2097,10 @@
     </row>
     <row r="39" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
@@ -2099,138 +2108,130 @@
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
       <c r="H39" s="1" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-      <c r="W39" s="1"/>
+      <c r="W39" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
     </row>
     <row r="40" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="3">
-        <v>14</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
-      <c r="H40" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
-      <c r="K40" s="3"/>
-      <c r="L40" s="3"/>
-      <c r="M40" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="N40" s="3"/>
-      <c r="O40" s="3"/>
-      <c r="P40" s="3"/>
-      <c r="Q40" s="3"/>
-      <c r="R40" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="S40" s="3"/>
-      <c r="T40" s="3"/>
-      <c r="U40" s="3"/>
-      <c r="V40" s="3"/>
-      <c r="W40" s="1"/>
-      <c r="X40" s="3"/>
-      <c r="Y40" s="3"/>
-      <c r="Z40" s="3"/>
-      <c r="AA40" s="3"/>
+      <c r="A40" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
     </row>
     <row r="41" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="3">
-        <v>15</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="H41" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I41" s="3"/>
-      <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3"/>
-      <c r="M41" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="N41" s="3"/>
-      <c r="O41" s="3"/>
-      <c r="P41" s="3"/>
-      <c r="Q41" s="3"/>
-      <c r="R41" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="S41" s="3"/>
-      <c r="T41" s="3"/>
-      <c r="U41" s="3"/>
-      <c r="V41" s="3"/>
-      <c r="W41" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="X41" s="3"/>
-      <c r="Y41" s="3"/>
-      <c r="Z41" s="3"/>
-      <c r="AA41" s="3"/>
-    </row>
-    <row r="42" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B42" s="11"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="11"/>
-    </row>
-    <row r="43" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="4" t="s">
+      <c r="A41" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B43" s="25" t="s">
+      <c r="B41" s="25" t="s">
         <v>7</v>
       </c>
+      <c r="C41" s="14"/>
+      <c r="D41" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="E41" s="14"/>
+      <c r="F41" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="G41" s="14"/>
+      <c r="I41" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="J41" s="11"/>
+      <c r="K41" s="11"/>
+      <c r="L41" s="11"/>
+      <c r="M41" s="11"/>
+      <c r="N41" s="11"/>
+      <c r="O41" s="11"/>
+      <c r="P41" s="11"/>
+      <c r="Q41" s="11"/>
+      <c r="S41" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="T41" s="11"/>
+      <c r="U41" s="11"/>
+      <c r="V41" s="11"/>
+      <c r="W41" s="11"/>
+      <c r="X41" s="11"/>
+      <c r="Y41" s="11"/>
+      <c r="Z41" s="11"/>
+      <c r="AA41" s="11"/>
+    </row>
+    <row r="42" spans="1:27" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="3">
+        <v>1</v>
+      </c>
+      <c r="B42" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C42" s="14"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="14"/>
+      <c r="I42" s="18">
+        <v>1</v>
+      </c>
+      <c r="J42" s="11"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="11"/>
+      <c r="M42" s="11"/>
+      <c r="N42" s="11"/>
+      <c r="O42" s="11"/>
+      <c r="P42" s="11"/>
+      <c r="Q42" s="11"/>
+      <c r="S42" s="18">
+        <v>1</v>
+      </c>
+      <c r="T42" s="11"/>
+      <c r="U42" s="11"/>
+      <c r="V42" s="11"/>
+      <c r="W42" s="11"/>
+      <c r="X42" s="11"/>
+      <c r="Y42" s="11"/>
+      <c r="Z42" s="11"/>
+      <c r="AA42" s="11"/>
+    </row>
+    <row r="43" spans="1:27" ht="62.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="3">
+        <v>2</v>
+      </c>
+      <c r="B43" s="24" t="s">
+        <v>28</v>
+      </c>
       <c r="C43" s="14"/>
-      <c r="D43" s="22" t="s">
-        <v>23</v>
-      </c>
+      <c r="D43" s="12"/>
       <c r="E43" s="14"/>
-      <c r="F43" s="26" t="s">
-        <v>24</v>
-      </c>
+      <c r="F43" s="12"/>
       <c r="G43" s="14"/>
-      <c r="I43" s="27" t="s">
-        <v>25</v>
+      <c r="I43" s="18" t="s">
+        <v>29</v>
       </c>
       <c r="J43" s="11"/>
       <c r="K43" s="11"/>
@@ -2240,8 +2241,8 @@
       <c r="O43" s="11"/>
       <c r="P43" s="11"/>
       <c r="Q43" s="11"/>
-      <c r="S43" s="27" t="s">
-        <v>26</v>
+      <c r="S43" s="18">
+        <v>2</v>
       </c>
       <c r="T43" s="11"/>
       <c r="U43" s="11"/>
@@ -2252,20 +2253,16 @@
       <c r="Z43" s="11"/>
       <c r="AA43" s="11"/>
     </row>
-    <row r="44" spans="1:27" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="3">
-        <v>1</v>
-      </c>
-      <c r="B44" s="23" t="s">
-        <v>27</v>
-      </c>
-      <c r="C44" s="14"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="12"/>
-      <c r="G44" s="14"/>
-      <c r="I44" s="10">
-        <v>1</v>
+    <row r="44" spans="1:27" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="5"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="21"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="21"/>
+      <c r="G44" s="11"/>
+      <c r="I44" s="18" t="s">
+        <v>30</v>
       </c>
       <c r="J44" s="11"/>
       <c r="K44" s="11"/>
@@ -2275,8 +2272,8 @@
       <c r="O44" s="11"/>
       <c r="P44" s="11"/>
       <c r="Q44" s="11"/>
-      <c r="S44" s="10">
-        <v>1</v>
+      <c r="S44" s="18">
+        <v>3</v>
       </c>
       <c r="T44" s="11"/>
       <c r="U44" s="11"/>
@@ -2287,20 +2284,16 @@
       <c r="Z44" s="11"/>
       <c r="AA44" s="11"/>
     </row>
-    <row r="45" spans="1:27" ht="62.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="3">
-        <v>2</v>
-      </c>
-      <c r="B45" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="C45" s="14"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="14"/>
-      <c r="I45" s="10" t="s">
-        <v>29</v>
+    <row r="45" spans="1:27" ht="95" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="5"/>
+      <c r="B45" s="21"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="21"/>
+      <c r="G45" s="11"/>
+      <c r="I45" s="18" t="s">
+        <v>31</v>
       </c>
       <c r="J45" s="11"/>
       <c r="K45" s="11"/>
@@ -2310,8 +2303,8 @@
       <c r="O45" s="11"/>
       <c r="P45" s="11"/>
       <c r="Q45" s="11"/>
-      <c r="S45" s="10">
-        <v>2</v>
+      <c r="S45" s="18" t="s">
+        <v>31</v>
       </c>
       <c r="T45" s="11"/>
       <c r="U45" s="11"/>
@@ -2322,194 +2315,18 @@
       <c r="Z45" s="11"/>
       <c r="AA45" s="11"/>
     </row>
-    <row r="46" spans="1:27" ht="72.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="5"/>
-      <c r="B46" s="24"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="24"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="24"/>
-      <c r="G46" s="11"/>
-      <c r="I46" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="J46" s="11"/>
-      <c r="K46" s="11"/>
-      <c r="L46" s="11"/>
-      <c r="M46" s="11"/>
-      <c r="N46" s="11"/>
-      <c r="O46" s="11"/>
-      <c r="P46" s="11"/>
-      <c r="Q46" s="11"/>
-      <c r="S46" s="10">
-        <v>3</v>
-      </c>
-      <c r="T46" s="11"/>
-      <c r="U46" s="11"/>
-      <c r="V46" s="11"/>
-      <c r="W46" s="11"/>
-      <c r="X46" s="11"/>
-      <c r="Y46" s="11"/>
-      <c r="Z46" s="11"/>
-      <c r="AA46" s="11"/>
-    </row>
-    <row r="47" spans="1:27" ht="95" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="5"/>
-      <c r="B47" s="24"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="24"/>
-      <c r="E47" s="11"/>
-      <c r="F47" s="24"/>
-      <c r="G47" s="11"/>
-      <c r="I47" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="J47" s="11"/>
-      <c r="K47" s="11"/>
-      <c r="L47" s="11"/>
-      <c r="M47" s="11"/>
-      <c r="N47" s="11"/>
-      <c r="O47" s="11"/>
-      <c r="P47" s="11"/>
-      <c r="Q47" s="11"/>
-      <c r="S47" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T47" s="11"/>
-      <c r="U47" s="11"/>
-      <c r="V47" s="11"/>
-      <c r="W47" s="11"/>
-      <c r="X47" s="11"/>
-      <c r="Y47" s="11"/>
-      <c r="Z47" s="11"/>
-      <c r="AA47" s="11"/>
-    </row>
-    <row r="48" spans="1:27" ht="25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="46" spans="1:27" ht="25" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <mergeCells count="148">
-    <mergeCell ref="A2:AA2"/>
-    <mergeCell ref="W21:Y21"/>
-    <mergeCell ref="P23:S23"/>
-    <mergeCell ref="P11:S11"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="T12:V12"/>
-    <mergeCell ref="T16:V16"/>
-    <mergeCell ref="T15:V15"/>
-    <mergeCell ref="L8:O8"/>
-    <mergeCell ref="T8:V8"/>
-    <mergeCell ref="W16:Y16"/>
-    <mergeCell ref="W18:Y18"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:K10"/>
-    <mergeCell ref="L10:O10"/>
-    <mergeCell ref="P10:S10"/>
-    <mergeCell ref="T10:V10"/>
-    <mergeCell ref="W10:Y10"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="S47:AA47"/>
-    <mergeCell ref="H4:V4"/>
+  <mergeCells count="142">
+    <mergeCell ref="T7:V7"/>
+    <mergeCell ref="W7:Y7"/>
+    <mergeCell ref="A5:AA5"/>
+    <mergeCell ref="W13:Y13"/>
+    <mergeCell ref="T23:V23"/>
+    <mergeCell ref="T17:V17"/>
+    <mergeCell ref="T20:V20"/>
+    <mergeCell ref="W19:Y19"/>
     <mergeCell ref="C21:G21"/>
-    <mergeCell ref="W23:Y23"/>
-    <mergeCell ref="H15:K15"/>
-    <mergeCell ref="L24:O24"/>
-    <mergeCell ref="H17:K17"/>
-    <mergeCell ref="I44:Q44"/>
-    <mergeCell ref="H21:K21"/>
-    <mergeCell ref="W14:Y14"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="W24:Y24"/>
-    <mergeCell ref="H9:K9"/>
-    <mergeCell ref="T9:V9"/>
-    <mergeCell ref="I45:Q45"/>
-    <mergeCell ref="W9:Y9"/>
-    <mergeCell ref="T6:V6"/>
-    <mergeCell ref="C24:G24"/>
-    <mergeCell ref="H11:K11"/>
-    <mergeCell ref="L14:O14"/>
-    <mergeCell ref="H22:K22"/>
-    <mergeCell ref="L22:O22"/>
-    <mergeCell ref="P22:S22"/>
-    <mergeCell ref="T22:V22"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="H18:K18"/>
-    <mergeCell ref="L12:O12"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="P14:S14"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="P21:S21"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="L18:O18"/>
-    <mergeCell ref="I46:Q46"/>
-    <mergeCell ref="S43:AA43"/>
-    <mergeCell ref="L23:O23"/>
-    <mergeCell ref="A42:D42"/>
-    <mergeCell ref="F44:G44"/>
-    <mergeCell ref="L16:O16"/>
-    <mergeCell ref="I43:Q43"/>
-    <mergeCell ref="L19:O19"/>
-    <mergeCell ref="W19:Y19"/>
-    <mergeCell ref="H20:K20"/>
-    <mergeCell ref="L20:O20"/>
-    <mergeCell ref="P20:S20"/>
-    <mergeCell ref="T20:V20"/>
-    <mergeCell ref="W22:Y22"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="P13:S13"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="F45:G45"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="I47:Q47"/>
-    <mergeCell ref="P17:S17"/>
-    <mergeCell ref="H16:K16"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="P12:S12"/>
-    <mergeCell ref="H12:K12"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="S44:AA44"/>
-    <mergeCell ref="W17:Y17"/>
-    <mergeCell ref="P19:S19"/>
-    <mergeCell ref="S46:AA46"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="S45:AA45"/>
-    <mergeCell ref="P24:S24"/>
-    <mergeCell ref="H24:K24"/>
-    <mergeCell ref="P9:S9"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="L17:O17"/>
-    <mergeCell ref="T17:V17"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="L13:O13"/>
-    <mergeCell ref="T13:V13"/>
-    <mergeCell ref="P18:S18"/>
-    <mergeCell ref="W12:Y12"/>
-    <mergeCell ref="H19:K19"/>
-    <mergeCell ref="H13:K13"/>
-    <mergeCell ref="P15:S15"/>
-    <mergeCell ref="H14:K14"/>
-    <mergeCell ref="L21:O21"/>
-    <mergeCell ref="L9:O9"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="A25:AA25"/>
-    <mergeCell ref="H23:K23"/>
-    <mergeCell ref="W15:Y15"/>
-    <mergeCell ref="T19:V19"/>
-    <mergeCell ref="T23:V23"/>
-    <mergeCell ref="T24:V24"/>
-    <mergeCell ref="T18:V18"/>
-    <mergeCell ref="T21:V21"/>
-    <mergeCell ref="W20:Y20"/>
-    <mergeCell ref="C22:G22"/>
     <mergeCell ref="L15:O15"/>
     <mergeCell ref="A3:AA3"/>
     <mergeCell ref="P16:S16"/>
@@ -2529,12 +2346,120 @@
     <mergeCell ref="L7:O7"/>
     <mergeCell ref="C8:G8"/>
     <mergeCell ref="W11:Y11"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="S43:AA43"/>
+    <mergeCell ref="P23:S23"/>
+    <mergeCell ref="H23:K23"/>
+    <mergeCell ref="P9:S9"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="L13:O13"/>
+    <mergeCell ref="T13:V13"/>
+    <mergeCell ref="P17:S17"/>
+    <mergeCell ref="W12:Y12"/>
+    <mergeCell ref="H18:K18"/>
+    <mergeCell ref="H13:K13"/>
+    <mergeCell ref="P15:S15"/>
+    <mergeCell ref="H14:K14"/>
+    <mergeCell ref="L20:O20"/>
+    <mergeCell ref="L9:O9"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="A24:AA24"/>
+    <mergeCell ref="H22:K22"/>
+    <mergeCell ref="F45:G45"/>
+    <mergeCell ref="P13:S13"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="F43:G43"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="I45:Q45"/>
+    <mergeCell ref="H16:K16"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="P12:S12"/>
+    <mergeCell ref="H12:K12"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="S42:AA42"/>
+    <mergeCell ref="P18:S18"/>
+    <mergeCell ref="S44:AA44"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="H17:K17"/>
+    <mergeCell ref="L12:O12"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="P14:S14"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="P20:S20"/>
+    <mergeCell ref="F41:G41"/>
+    <mergeCell ref="L17:O17"/>
+    <mergeCell ref="I44:Q44"/>
+    <mergeCell ref="S41:AA41"/>
+    <mergeCell ref="L22:O22"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="F42:G42"/>
+    <mergeCell ref="L16:O16"/>
+    <mergeCell ref="I41:Q41"/>
+    <mergeCell ref="L18:O18"/>
+    <mergeCell ref="W18:Y18"/>
+    <mergeCell ref="H19:K19"/>
+    <mergeCell ref="L19:O19"/>
+    <mergeCell ref="P19:S19"/>
+    <mergeCell ref="T19:V19"/>
+    <mergeCell ref="W21:Y21"/>
+    <mergeCell ref="S45:AA45"/>
+    <mergeCell ref="H4:V4"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="W22:Y22"/>
+    <mergeCell ref="H15:K15"/>
+    <mergeCell ref="L23:O23"/>
+    <mergeCell ref="I42:Q42"/>
+    <mergeCell ref="H20:K20"/>
+    <mergeCell ref="W14:Y14"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="W23:Y23"/>
+    <mergeCell ref="H9:K9"/>
+    <mergeCell ref="T9:V9"/>
+    <mergeCell ref="I43:Q43"/>
+    <mergeCell ref="W9:Y9"/>
+    <mergeCell ref="T6:V6"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="H11:K11"/>
+    <mergeCell ref="L14:O14"/>
+    <mergeCell ref="H21:K21"/>
+    <mergeCell ref="L21:O21"/>
+    <mergeCell ref="P21:S21"/>
+    <mergeCell ref="T21:V21"/>
+    <mergeCell ref="A2:AA2"/>
+    <mergeCell ref="W20:Y20"/>
+    <mergeCell ref="P22:S22"/>
+    <mergeCell ref="P11:S11"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="T12:V12"/>
+    <mergeCell ref="T16:V16"/>
+    <mergeCell ref="T15:V15"/>
+    <mergeCell ref="L8:O8"/>
+    <mergeCell ref="T8:V8"/>
+    <mergeCell ref="W16:Y16"/>
+    <mergeCell ref="W17:Y17"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="H10:K10"/>
+    <mergeCell ref="L10:O10"/>
+    <mergeCell ref="P10:S10"/>
+    <mergeCell ref="T10:V10"/>
+    <mergeCell ref="W10:Y10"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="W15:Y15"/>
+    <mergeCell ref="T18:V18"/>
+    <mergeCell ref="T22:V22"/>
     <mergeCell ref="W8:Y8"/>
     <mergeCell ref="P7:S7"/>
-    <mergeCell ref="T7:V7"/>
-    <mergeCell ref="W7:Y7"/>
-    <mergeCell ref="A5:AA5"/>
-    <mergeCell ref="W13:Y13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
